--- a/artfynd/A 62350-2025 artfynd.xlsx
+++ b/artfynd/A 62350-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132236637</v>
       </c>
       <c r="B2" t="n">
-        <v>92147</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62350-2025 artfynd.xlsx
+++ b/artfynd/A 62350-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132236637</v>
       </c>
       <c r="B2" t="n">
-        <v>92183</v>
+        <v>92188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62350-2025 artfynd.xlsx
+++ b/artfynd/A 62350-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132236637</v>
       </c>
       <c r="B2" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62350-2025 artfynd.xlsx
+++ b/artfynd/A 62350-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132236637</v>
       </c>
       <c r="B2" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62350-2025 artfynd.xlsx
+++ b/artfynd/A 62350-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132236637</v>
       </c>
       <c r="B2" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62350-2025 artfynd.xlsx
+++ b/artfynd/A 62350-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132236637</v>
       </c>
       <c r="B2" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
